--- a/simulations/PARETO/Résultat avec contrainte/CO2_EQ_ss_inv.xlsx
+++ b/simulations/PARETO/Résultat avec contrainte/CO2_EQ_ss_inv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\PARETO\Résultat avec contrainte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906AD286-D180-4121-B582-A112F222F839}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB741B0-0F94-4485-9AAD-A3AC6D3519DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -180,6 +180,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0E+00"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -259,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -278,6 +281,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -287,9 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1744,41 +1748,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="37" max="37" width="10.90625" customWidth="1"/>
+    <col min="38" max="38" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="8" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="9"/>
+      <c r="AA1" s="10"/>
       <c r="AB1" s="2" t="s">
         <v>2</v>
       </c>
@@ -2212,6 +2220,26 @@
       <c r="AN7">
         <f t="shared" si="2"/>
         <v>70.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AK10" s="12">
+        <f>(AD3-AD6)/AD3</f>
+        <v>-0.33611123255310382</v>
+      </c>
+      <c r="AL10" s="4">
+        <f>(AG3-AG6)/AG3</f>
+        <v>0.16381636260878135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AK12" s="4">
+        <f>(AD7-AD6)/AD6</f>
+        <v>1.0050458804024143</v>
+      </c>
+      <c r="AL12" s="4">
+        <f>(AG7-AG6)/AG6</f>
+        <v>-2.1890591099456982</v>
       </c>
     </row>
   </sheetData>
@@ -2260,10 +2288,10 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="8">
         <v>91256.49</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="8">
         <v>126329.53</v>
       </c>
       <c r="D2">
@@ -2274,10 +2302,10 @@
       <c r="A3">
         <v>0.25</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>91256.49</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>126329.53</v>
       </c>
       <c r="D3">
@@ -2288,13 +2316,13 @@
       <c r="A4">
         <v>0.5</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="8">
         <v>186611.81</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>117168.48</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="8">
         <v>2782.4</v>
       </c>
     </row>
@@ -2302,10 +2330,10 @@
       <c r="A5">
         <v>0.75</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <v>186611.81</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>185060.41</v>
       </c>
       <c r="D5">
@@ -2322,16 +2350,16 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="8">
         <v>186611.81</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>185060.41</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="8">
         <v>516.9</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="8">
         <v>2265.5</v>
       </c>
     </row>
